--- a/customer_profiles/shefish/templates/sk/pi.xlsx
+++ b/customer_profiles/shefish/templates/sk/pi.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21570" windowHeight="10387" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="10005" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name=" Standard PI format" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">' Standard PI format'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">' Standard PI format'!$A$1:$H$18</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="169" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="48">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -53,6 +53,18 @@
       <sz val="16"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
       <color rgb="FF00B0F0"/>
@@ -62,18 +74,6 @@
       <name val="Arial"/>
       <charset val="134"/>
       <color theme="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -341,12 +341,6 @@
       <i val="1"/>
       <color indexed="23"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -1246,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1293,21 +1287,32 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1322,37 +1327,227 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="84">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="77">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="77">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
@@ -1367,6 +1562,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1382,21 +1580,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="77">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="77">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1406,26 +1602,8 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1433,282 +1611,45 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="84">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="117">
@@ -2204,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="11.6"/>
   <cols>
     <col width="17.75" customWidth="1" style="3" min="1" max="1"/>
@@ -2219,411 +2160,434 @@
     <col width="9" customWidth="1" style="3" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="74">
-      <c r="A1" s="75" t="inlineStr">
+    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="72">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
         </is>
       </c>
-      <c r="I1" s="76" t="n"/>
-      <c r="J1" s="76" t="n"/>
-    </row>
-    <row r="2" ht="15" customFormat="1" customHeight="1" s="74">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="I1" s="74" t="n"/>
+      <c r="J1" s="74" t="n"/>
+    </row>
+    <row r="2" ht="15" customFormat="1" customHeight="1" s="72">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>NO.40 BAIJIA STREET HIGH-TECH INDUSTRIAL DEVELOPMENT ZONE QINGYUAN GUANGDONG CHINA</t>
         </is>
       </c>
-      <c r="I2" s="76" t="n"/>
-      <c r="J2" s="76" t="n"/>
-    </row>
-    <row r="3" ht="15" customFormat="1" customHeight="1" s="74">
-      <c r="A3" s="78" t="n"/>
-      <c r="B3" s="78" t="n"/>
-      <c r="C3" s="78" t="n"/>
-      <c r="D3" s="78" t="n"/>
-      <c r="E3" s="78" t="n"/>
-      <c r="F3" s="78" t="n"/>
-      <c r="G3" s="78" t="n"/>
-      <c r="H3" s="78" t="n"/>
-      <c r="I3" s="76" t="n"/>
-      <c r="J3" s="76" t="n"/>
-    </row>
-    <row r="4" ht="15" customFormat="1" customHeight="1" s="74">
-      <c r="A4" s="79" t="inlineStr">
+      <c r="I2" s="74" t="n"/>
+      <c r="J2" s="74" t="n"/>
+    </row>
+    <row r="3" ht="15" customFormat="1" customHeight="1" s="72">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="76" t="n"/>
+      <c r="C3" s="76" t="n"/>
+      <c r="D3" s="76" t="n"/>
+      <c r="E3" s="76" t="n"/>
+      <c r="F3" s="76" t="n"/>
+      <c r="G3" s="76" t="n"/>
+      <c r="H3" s="76" t="n"/>
+      <c r="I3" s="74" t="n"/>
+      <c r="J3" s="74" t="n"/>
+    </row>
+    <row r="4" ht="15" customFormat="1" customHeight="1" s="72">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>PROFORMA INVOICE</t>
         </is>
       </c>
-      <c r="I4" s="76" t="n"/>
-      <c r="J4" s="76" t="n"/>
-    </row>
-    <row r="5" ht="15.95" customFormat="1" customHeight="1" s="74">
-      <c r="A5" s="80" t="n"/>
+      <c r="I4" s="74" t="n"/>
+      <c r="J4" s="74" t="n"/>
+    </row>
+    <row r="5" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A5" s="78" t="n"/>
       <c r="B5" s="10" t="n"/>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="82" t="n"/>
+      <c r="E5" s="79" t="n"/>
+      <c r="F5" s="80" t="n"/>
       <c r="G5" s="13" t="n"/>
       <c r="H5" s="13" t="n"/>
-      <c r="I5" s="76" t="n"/>
-      <c r="J5" s="76" t="n"/>
-    </row>
-    <row r="6" ht="17" customFormat="1" customHeight="1" s="74">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="I5" s="74" t="n"/>
+      <c r="J5" s="74" t="n"/>
+    </row>
+    <row r="6" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A6" s="78" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="E6" s="79" t="n"/>
+      <c r="F6" s="81" t="inlineStr">
+        <is>
+          <t>PI Number:</t>
+        </is>
+      </c>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="83" t="n"/>
+      <c r="I6" s="74" t="n"/>
+      <c r="J6" s="74" t="n"/>
+    </row>
+    <row r="7" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A7" s="78" t="inlineStr">
         <is>
           <t>Incoterm:</t>
         </is>
       </c>
-      <c r="B6" s="141" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>DDP USA</t>
         </is>
       </c>
-      <c r="F6" s="82" t="inlineStr">
+      <c r="C7" s="84" t="n"/>
+      <c r="D7" s="85" t="n"/>
+      <c r="F7" s="80" t="inlineStr">
         <is>
           <t>PO Number:</t>
         </is>
       </c>
-      <c r="G6" s="85" t="n"/>
-      <c r="H6" s="104" t="n"/>
-      <c r="I6" s="76" t="n"/>
-      <c r="J6" s="76" t="n"/>
-    </row>
-    <row r="7" ht="17" customFormat="1" customHeight="1" s="74">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="G7" s="86" t="n"/>
+      <c r="H7" s="84" t="n"/>
+      <c r="I7" s="74" t="n"/>
+      <c r="J7" s="74" t="n"/>
+    </row>
+    <row r="8" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>Payment Terms:</t>
         </is>
       </c>
-      <c r="B7" s="141" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Net 60 days</t>
         </is>
       </c>
-      <c r="F7" s="82" t="inlineStr">
+      <c r="C8" s="84" t="n"/>
+      <c r="D8" s="85" t="n"/>
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>Document Date:</t>
         </is>
       </c>
-      <c r="G7" s="86" t="n"/>
-      <c r="H7" s="109" t="n"/>
-      <c r="I7" s="76" t="n"/>
-      <c r="J7" s="76" t="n"/>
-    </row>
-    <row r="8" ht="15.95" customFormat="1" customHeight="1" s="74">
-      <c r="A8" s="87" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="G8" s="88" t="n"/>
-      <c r="H8" s="89" t="n"/>
-      <c r="I8" s="76" t="n"/>
-      <c r="J8" s="76" t="n"/>
-    </row>
-    <row r="9" ht="17" customFormat="1" customHeight="1" s="74">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="G8" s="87" t="n"/>
+      <c r="H8" s="84" t="n"/>
+      <c r="I8" s="74" t="n"/>
+      <c r="J8" s="74" t="n"/>
+    </row>
+    <row r="9" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A9" s="88" t="n"/>
+      <c r="E9" s="79" t="n"/>
+      <c r="G9" s="89" t="n"/>
+      <c r="H9" s="90" t="n"/>
+      <c r="I9" s="74" t="n"/>
+      <c r="J9" s="74" t="n"/>
+    </row>
+    <row r="10" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A10" s="88" t="inlineStr">
         <is>
           <t>Bill To:</t>
         </is>
       </c>
-      <c r="B9" s="137" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>GLOBALSINO PTE.LTD.</t>
         </is>
       </c>
-      <c r="C9" s="94" t="n"/>
-      <c r="D9" s="94" t="n"/>
-      <c r="E9" s="92" t="n"/>
-      <c r="F9" s="88" t="inlineStr">
+      <c r="C10" s="92" t="n"/>
+      <c r="D10" s="84" t="n"/>
+      <c r="E10" s="93" t="n"/>
+      <c r="F10" s="89" t="inlineStr">
         <is>
           <t>Ship to:</t>
         </is>
       </c>
-      <c r="G9" s="93" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>GLOBALSINO PTE.LTD.</t>
         </is>
       </c>
-      <c r="H9" s="94" t="n"/>
-      <c r="I9" s="83" t="n"/>
-      <c r="J9" s="76" t="n"/>
-    </row>
-    <row r="10" ht="15.95" customFormat="1" customHeight="1" s="74">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="96" t="n"/>
-      <c r="C10" s="97" t="n"/>
-      <c r="D10" s="92" t="n"/>
-      <c r="E10" s="92" t="n"/>
-      <c r="G10" s="96" t="n"/>
-      <c r="H10" s="97" t="n"/>
-      <c r="I10" s="76" t="n"/>
-      <c r="J10" s="76" t="n"/>
-    </row>
-    <row r="11" ht="15.95" customFormat="1" customHeight="1" s="98">
-      <c r="A11" s="87" t="n"/>
-      <c r="B11" s="96" t="n"/>
-      <c r="C11" s="97" t="n"/>
-      <c r="D11" s="99" t="n"/>
-      <c r="E11" s="92" t="n"/>
-      <c r="G11" s="96" t="n"/>
-      <c r="H11" s="97" t="n"/>
-      <c r="I11" s="100" t="n"/>
-      <c r="J11" s="100" t="n"/>
-    </row>
-    <row r="12" ht="15.95" customFormat="1" customHeight="1" s="98">
-      <c r="A12" s="87" t="n"/>
-      <c r="B12" s="92" t="n"/>
+      <c r="H10" s="92" t="n"/>
+      <c r="I10" s="84" t="n"/>
+      <c r="J10" s="74" t="n"/>
+    </row>
+    <row r="11" ht="15.95" customFormat="1" customHeight="1" s="72">
+      <c r="A11" s="94" t="n"/>
+      <c r="B11" s="91" t="n"/>
+      <c r="C11" s="92" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="G11" s="91" t="n"/>
+      <c r="H11" s="92" t="n"/>
+      <c r="I11" s="74" t="n"/>
+      <c r="J11" s="74" t="n"/>
+    </row>
+    <row r="12" ht="15.95" customFormat="1" customHeight="1" s="95">
+      <c r="A12" s="88" t="n"/>
+      <c r="B12" s="91" t="n"/>
       <c r="C12" s="92" t="n"/>
-      <c r="D12" s="92" t="n"/>
-      <c r="E12" s="92" t="n"/>
-      <c r="G12" s="88" t="n"/>
-      <c r="H12" s="101" t="n"/>
-      <c r="I12" s="100" t="n"/>
-      <c r="J12" s="100" t="n"/>
-    </row>
-    <row r="13" ht="29" customFormat="1" customHeight="1" s="98">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="G12" s="91" t="n"/>
+      <c r="H12" s="92" t="n"/>
+      <c r="I12" s="96" t="n"/>
+      <c r="J12" s="96" t="n"/>
+    </row>
+    <row r="13" ht="15.95" customFormat="1" customHeight="1" s="95">
+      <c r="A13" s="88" t="n"/>
+      <c r="B13" s="93" t="n"/>
+      <c r="C13" s="93" t="n"/>
+      <c r="D13" s="93" t="n"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="G13" s="89" t="n"/>
+      <c r="H13" s="97" t="n"/>
+      <c r="I13" s="96" t="n"/>
+      <c r="J13" s="96" t="n"/>
+    </row>
+    <row r="14" ht="25.5" customFormat="1" customHeight="1" s="95">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>Port of Loading:</t>
         </is>
       </c>
-      <c r="B13" s="142" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>Qingdao, China</t>
         </is>
       </c>
-      <c r="E13" s="92" t="n"/>
-      <c r="F13" s="82" t="inlineStr">
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="93" t="n"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="80" t="inlineStr">
         <is>
           <t>Actual Manufacturer Company Name</t>
         </is>
       </c>
-      <c r="G13" s="103" t="inlineStr">
+      <c r="G14" s="99" t="inlineStr">
         <is>
           <t>GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
         </is>
       </c>
-      <c r="H13" s="104" t="n"/>
-      <c r="I13" s="83" t="n"/>
-      <c r="J13" s="100" t="n"/>
-    </row>
-    <row r="14" ht="17" customFormat="1" customHeight="1" s="98">
-      <c r="A14" s="80" t="inlineStr">
+      <c r="H14" s="100" t="n"/>
+      <c r="I14" s="84" t="n"/>
+      <c r="J14" s="96" t="n"/>
+    </row>
+    <row r="15" ht="15.95" customFormat="1" customHeight="1" s="95">
+      <c r="A15" s="78" t="inlineStr">
         <is>
           <t>Final Destination</t>
         </is>
       </c>
-      <c r="B14" s="143" t="inlineStr">
+      <c r="B15" s="101" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E14" s="92" t="n"/>
-      <c r="F14" s="82" t="inlineStr">
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>Actual Manufacturer Company Address</t>
         </is>
       </c>
-      <c r="G14" s="103" t="inlineStr">
+      <c r="G15" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">NO.40 BAIJIA STREET </t>
         </is>
       </c>
-      <c r="H14" s="104" t="n"/>
-      <c r="I14" s="83" t="n"/>
-      <c r="J14" s="100" t="n"/>
-    </row>
-    <row r="15" ht="29" customFormat="1" customHeight="1" s="98">
-      <c r="A15" s="87" t="n"/>
-      <c r="B15" s="92" t="n"/>
-      <c r="C15" s="92" t="n"/>
-      <c r="D15" s="92" t="n"/>
-      <c r="E15" s="92" t="n"/>
-      <c r="G15" s="108" t="inlineStr">
+      <c r="H15" s="103" t="n"/>
+      <c r="I15" s="84" t="n"/>
+      <c r="J15" s="96" t="n"/>
+    </row>
+    <row r="16" ht="24" customFormat="1" customHeight="1" s="95">
+      <c r="A16" s="88" t="n"/>
+      <c r="B16" s="93" t="n"/>
+      <c r="C16" s="93" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="G16" s="104" t="inlineStr">
         <is>
           <t>HIGH-TECH INDUSTRIAL DEVELOPMENT ZONE QINGYUAN GUANGDONG CHINA</t>
         </is>
       </c>
-      <c r="H15" s="109" t="n"/>
-      <c r="I15" s="100" t="n"/>
-      <c r="J15" s="100" t="n"/>
-    </row>
-    <row r="16" ht="7" customHeight="1" s="110">
-      <c r="A16" s="111" t="n"/>
-      <c r="B16" s="112" t="n"/>
-      <c r="C16" s="112" t="n"/>
-      <c r="D16" s="112" t="n"/>
-      <c r="E16" s="112" t="n"/>
-      <c r="F16" s="112" t="n"/>
-      <c r="G16" s="112" t="n"/>
-      <c r="H16" s="112" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="110">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="H16" s="105" t="n"/>
+      <c r="I16" s="96" t="n"/>
+      <c r="J16" s="96" t="n"/>
+    </row>
+    <row r="17" ht="50" customHeight="1" s="106">
+      <c r="A17" s="107" t="n"/>
+      <c r="B17" s="108" t="n"/>
+      <c r="C17" s="108" t="n"/>
+      <c r="D17" s="108" t="n"/>
+      <c r="E17" s="108" t="n"/>
+      <c r="F17" s="108" t="n"/>
+      <c r="G17" s="108" t="n"/>
+      <c r="H17" s="108" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="106">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Country of The Origin</t>
         </is>
       </c>
-      <c r="B17" s="113" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>Item Number</t>
         </is>
       </c>
-      <c r="C17" s="113" t="inlineStr">
+      <c r="C18" s="109" t="inlineStr">
         <is>
           <t>UPC</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Description </t>
         </is>
       </c>
-      <c r="E17" s="114" t="inlineStr">
+      <c r="E18" s="110" t="inlineStr">
         <is>
           <t>USD Unit Price</t>
         </is>
       </c>
-      <c r="F17" s="113" t="inlineStr">
+      <c r="F18" s="109" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G17" s="115" t="inlineStr">
+      <c r="G18" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">USD Amount </t>
         </is>
       </c>
-      <c r="H17" s="116" t="inlineStr">
+      <c r="H18" s="112" t="inlineStr">
         <is>
           <t>EX-FACTORY DATE</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="110">
-      <c r="A18" s="53" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="117" t="n"/>
-      <c r="D18" s="140" t="n"/>
-      <c r="E18" s="118" t="n"/>
-      <c r="F18" s="119" t="n"/>
-      <c r="G18" s="144" t="n"/>
-      <c r="H18" s="145" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="110">
-      <c r="A19" s="53" t="n"/>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="117" t="n"/>
-      <c r="D19" s="140" t="n"/>
-      <c r="E19" s="118" t="n"/>
-      <c r="F19" s="119" t="n"/>
-      <c r="G19" s="144" t="n"/>
-      <c r="H19" s="145" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="110">
-      <c r="A20" s="53" t="n"/>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="117" t="n"/>
-      <c r="D20" s="140" t="n"/>
-      <c r="E20" s="118" t="n"/>
-      <c r="F20" s="119" t="n"/>
-      <c r="G20" s="144" t="n"/>
-      <c r="H20" s="145" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1" s="110">
-      <c r="A21" s="53" t="n"/>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="117" t="n"/>
-      <c r="D21" s="140" t="n"/>
-      <c r="E21" s="118" t="n"/>
-      <c r="F21" s="119" t="n"/>
-      <c r="G21" s="144" t="n"/>
-      <c r="H21" s="145" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1" s="110">
-      <c r="A22" s="122" t="n"/>
-      <c r="B22" s="123" t="n"/>
-      <c r="C22" s="123" t="n"/>
-      <c r="D22" s="124" t="n"/>
-      <c r="E22" s="125" t="inlineStr">
+    <row r="19" ht="18" customHeight="1" s="106">
+      <c r="A19" s="46" t="n"/>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="113" t="n"/>
+      <c r="F19" s="51" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="114" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="106">
+      <c r="A20" s="46" t="n"/>
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="113" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="114" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="106">
+      <c r="A21" s="46" t="n"/>
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="113" t="n"/>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="114" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="106">
+      <c r="A22" s="46" t="n"/>
+      <c r="B22" s="47" t="n"/>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="113" t="n"/>
+      <c r="F22" s="51" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="114" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" s="106">
+      <c r="A23" s="115" t="n"/>
+      <c r="B23" s="116" t="n"/>
+      <c r="C23" s="116" t="n"/>
+      <c r="D23" s="117" t="n"/>
+      <c r="E23" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">Sub-Total </t>
         </is>
       </c>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="100" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1" s="110">
-      <c r="A23" s="126" t="n"/>
-      <c r="B23" s="126" t="n"/>
-      <c r="C23" s="126" t="n"/>
-      <c r="D23" s="126" t="n"/>
-      <c r="E23" s="127" t="n"/>
-      <c r="F23" s="128" t="inlineStr">
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="59" t="n"/>
+      <c r="H23" s="96" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" s="106">
+      <c r="A24" s="119" t="n"/>
+      <c r="B24" s="119" t="n"/>
+      <c r="C24" s="119" t="n"/>
+      <c r="D24" s="119" t="n"/>
+      <c r="E24" s="120" t="n"/>
+      <c r="F24" s="121" t="inlineStr">
         <is>
           <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
         </is>
       </c>
-      <c r="G23" s="66" t="n"/>
-      <c r="H23" s="129" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1" s="110">
-      <c r="A24" s="127" t="n"/>
-      <c r="B24" s="127" t="n"/>
-      <c r="C24" s="127" t="n"/>
-      <c r="D24" s="127" t="n"/>
-      <c r="E24" s="127" t="n"/>
-      <c r="F24" s="127" t="n"/>
-      <c r="G24" s="127" t="n"/>
-      <c r="H24" s="129" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1" s="110">
-      <c r="A25" s="130" t="n"/>
-      <c r="B25" s="127" t="n"/>
-      <c r="C25" s="127" t="n"/>
-      <c r="D25" s="127" t="n"/>
-      <c r="E25" s="131" t="inlineStr">
+      <c r="G24" s="64" t="n"/>
+      <c r="H24" s="122" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1" s="106">
+      <c r="A25" s="120" t="n"/>
+      <c r="B25" s="120" t="n"/>
+      <c r="C25" s="120" t="n"/>
+      <c r="D25" s="120" t="n"/>
+      <c r="E25" s="120" t="n"/>
+      <c r="F25" s="120" t="n"/>
+      <c r="G25" s="120" t="n"/>
+      <c r="H25" s="122" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1" s="106">
+      <c r="A26" s="123" t="n"/>
+      <c r="B26" s="120" t="n"/>
+      <c r="C26" s="120" t="n"/>
+      <c r="D26" s="120" t="n"/>
+      <c r="E26" s="124" t="inlineStr">
         <is>
           <t>Signature:</t>
         </is>
       </c>
-      <c r="F25" s="132" t="n"/>
-      <c r="G25" s="132" t="n"/>
-      <c r="H25" s="83" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1" s="110">
-      <c r="A26" s="130" t="n"/>
-      <c r="B26" s="127" t="n"/>
-      <c r="C26" s="127" t="n"/>
-      <c r="D26" s="127" t="n"/>
-      <c r="E26" s="133" t="inlineStr">
+      <c r="F26" s="125" t="n"/>
+      <c r="G26" s="125" t="n"/>
+      <c r="H26" s="84" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1" s="106">
+      <c r="A27" s="123" t="n"/>
+      <c r="B27" s="120" t="n"/>
+      <c r="C27" s="120" t="n"/>
+      <c r="D27" s="120" t="n"/>
+      <c r="E27" s="126" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="F26" s="134" t="n"/>
-      <c r="G26" s="135" t="n"/>
-      <c r="H26" s="83" t="n"/>
+      <c r="F27" s="127" t="n"/>
+      <c r="G27" s="128" t="n"/>
+      <c r="H27" s="84" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G6:H6"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B19">
+    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
+  <conditionalFormatting sqref="B20:B22">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.196850393700787" right="0.236220472440945" top="0.47244094488189" bottom="0.511811023622047" header="0.236220472440945" footer="0.196850393700787"/>
   <pageSetup orientation="portrait" paperSize="1" scale="73" verticalDpi="203"/>
